--- a/restructure/data/battery_info.xlsx
+++ b/restructure/data/battery_info.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1152"/>
+  <dimension ref="A1:H1368"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -46153,6 +46153,8646 @@
         </is>
       </c>
     </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1153" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1153" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1153" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1154" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1154" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1154" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1155" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1155" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1155" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1156" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1156" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1156" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>2024-04-07</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1157" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1157" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1157" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>2024-04-07</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1158" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1158" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1158" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1159" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1159" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1159" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>01:30:00</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1160" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1160" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1160" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1161" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1161" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1161" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1162" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1162" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1162" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1163" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1163" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1164" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1164" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>charging;</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1165" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1165" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1166" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1166" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1167" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1167" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1167" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1168" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1168" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1168" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1169" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1169" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1169" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>01:30:00</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1170" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1170" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1170" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1171" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1171" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1171" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>finishing</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1172" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1172" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1172" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1173" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1173" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1173" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>21:00:01</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1174" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1174" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1174" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1175" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1175" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1175" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1176" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1176" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1176" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1177" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1177" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1177" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>21:00:01</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1178" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1178" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1178" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1179" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1179" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1179" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>01:30:00</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1180" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1180" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1180" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1181" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1181" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1181" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>finishing</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1182" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1182" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1182" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1183" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1183" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1183" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1184" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1184" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1184" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1185" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1185" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1185" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1186" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1186" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1186" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>finishing</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1187" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1187" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1187" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1188" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1188" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1188" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>charging;</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1189" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1189" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1189" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1190" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1190" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1190" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1191" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1191" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1191" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>09:00:01</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1192" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1192" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1192" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>charging;</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1193" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1193" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1193" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1194" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1194" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1194" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1195" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1195" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1195" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>2024-04-18</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1196" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1196" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1196" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>2024-04-18</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1197" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1197" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1197" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>2024-04-18</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1198" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1198" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1198" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>2024-04-18</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1199" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1199" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1199" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>2024-04-18</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1200" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1200" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1200" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1201" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1201" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1201" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1202" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1202" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1202" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1203" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1203" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1203" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1204" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1204" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1204" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>charging;</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1205" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1205" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1205" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1206" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1206" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1206" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1207" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1207" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1207" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>2024-04-21</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1208" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1208" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1208" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>2024-04-22</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>charging;</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1209" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1209" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1209" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>2024-04-22</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>01:30:00</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1210" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1210" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1210" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>2024-04-22</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1211" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1211" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1211" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>01:30:00</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1212" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1212" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1212" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>finishing</t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1213" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1213" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1213" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1214" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1214" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1214" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1215" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1215" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1215" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1216" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1216" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1216" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>00:00:01</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1217" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1217" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1217" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1218" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1218" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1218" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>01:30:00</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1219" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1219" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1219" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1220" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1220" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1220" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>2024-04-26</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1221" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1221" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1221" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>2024-04-26</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>charging;</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1222" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1222" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>2024-04-26</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>21:00:01</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1223" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1223" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1223" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>2024-04-27</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1224" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1224" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1224" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>2024-04-27</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1225" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1225" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1225" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>2024-04-28</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1226" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1226" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1226" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>2024-04-28</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1227" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1227" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1227" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1228" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1228" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1228" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1228" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1229" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1229" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1229" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>charging;</t>
+        </is>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1230" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1230" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1230" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1231" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1231" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1231" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1232" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1232" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1232" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1232" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>finishing</t>
+        </is>
+      </c>
+      <c r="E1233" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1233" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1233" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1233" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1234" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1234" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1234" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1234" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>charging;</t>
+        </is>
+      </c>
+      <c r="E1235" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1235" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1235" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1235" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1236" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1236" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1236" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1237" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1237" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1237" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1237" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1238" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1238" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1238" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1239" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1239" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1239" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>01:30:00</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1240" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1240" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1240" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>charging;</t>
+        </is>
+      </c>
+      <c r="E1241" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1241" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1241" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1241" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1242" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1242" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1242" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1242" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1243" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1243" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1243" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1244" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1244" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1244" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1245" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1245" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1245" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>charging;</t>
+        </is>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1246" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1246" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1246" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1247" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1247" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1247" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1248" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1248" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1248" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1249" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1249" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1249" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1250" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1250" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1250" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1251" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1251" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1251" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1252" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1252" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1252" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>2024-05-12</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1253" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1253" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1253" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>12:00:01</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>charging;</t>
+        </is>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1254" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1254" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1254" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>charging;</t>
+        </is>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1255" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1255" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1255" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1256" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1256" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1256" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1257" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1257" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1257" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1258" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1258" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1258" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1258" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>01:30:00</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1259" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1259" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1259" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1259" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1260" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1260" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1260" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1260" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1261" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1261" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1261" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1262" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1262" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1262" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1263" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1263" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1263" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1264" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1264" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1264" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1265" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1265" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1265" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1266" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1266" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1266" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1267" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1267" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1267" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1268" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1268" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1268" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1268" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>01:30:00</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1269" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1269" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1269" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1269" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1270" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1270" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1270" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1270" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>2024-05-19</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1271" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1271" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1271" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1271" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>2024-05-20</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1272" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1272" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1272" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1273" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1273" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1273" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1273" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1274" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1274" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1274" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1274" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1275" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1275" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1275" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>01:30:00</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>charging;</t>
+        </is>
+      </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1276" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1276" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1276" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1277" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1277" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1277" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1277" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1278" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1278" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1278" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1278" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>Unplugged</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1279" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1279" t="n">
+        <v>60</v>
+      </c>
+      <c r="G1279" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1279" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1280" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1280" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1280" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1280" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>2024-05-25</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1281" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1281" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1281" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>2024-05-25</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1282" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1282" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1282" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>2024-05-25</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1283" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1283" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1283" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1283" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1284" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1284" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1284" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1284" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1285" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1285" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1285" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1285" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1286" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1286" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1286" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1286" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>2024-05-27</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1287" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1287" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1287" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1287" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>2024-05-27</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1288" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1288" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1288" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>2024-05-27</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1289" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1289" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1289" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1289" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>2024-05-27</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1290" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1290" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1290" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1291" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1291" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1291" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1291" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>charging;</t>
+        </is>
+      </c>
+      <c r="E1292" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1292" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1292" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1292" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1293" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1293" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1293" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1293" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1294" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1294" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1294" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1294" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>01:30:00</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>charging;</t>
+        </is>
+      </c>
+      <c r="E1295" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1295" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1295" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1295" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1296" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1296" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1296" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1296" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1297" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1297" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1297" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1297" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1298" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1298" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1298" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1298" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>01:30:00</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1299" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1299" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1299" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1299" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>charging;</t>
+        </is>
+      </c>
+      <c r="E1300" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1300" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1300" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1300" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1301" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1301" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1301" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1301" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1302" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1302" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1302" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>charging;</t>
+        </is>
+      </c>
+      <c r="E1303" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1303" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1303" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1303" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>2024-06-02</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1304" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1304" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1304" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1304" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>finishing</t>
+        </is>
+      </c>
+      <c r="E1305" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1305" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1305" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1305" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1306" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1306" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1306" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1306" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1307" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1307" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1307" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1307" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>finishing</t>
+        </is>
+      </c>
+      <c r="E1308" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1308" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1308" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1308" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1309" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1309" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1309" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1309" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1310" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1310" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1310" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1310" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1311" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1311" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1311" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1311" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1312" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1312" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1312" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1312" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>charging;</t>
+        </is>
+      </c>
+      <c r="E1313" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1313" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1313" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1313" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1314" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1314" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1314" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1314" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>18:00:01</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1315" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1315" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1315" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1315" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1316" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1316" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1316" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1317" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1317" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1317" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1317" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1318" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1318" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1318" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1318" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>finishing</t>
+        </is>
+      </c>
+      <c r="E1319" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1319" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1319" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1319" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1320" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1320" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1320" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1320" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1321" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1321" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1321" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1322" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1322" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1322" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1322" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1323" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1323" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1323" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1323" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>01:30:00</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1324" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1324" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1324" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1324" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>charging;</t>
+        </is>
+      </c>
+      <c r="E1325" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1325" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1325" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1325" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1326" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1326" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1326" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1326" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1327" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1327" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1327" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1327" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1328" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1328" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1328" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1328" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1329" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1329" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1329" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1329" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>charging;</t>
+        </is>
+      </c>
+      <c r="E1330" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1330" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1330" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1330" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1331" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1331" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1331" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1331" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1332" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1332" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1332" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1332" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1333" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1333" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1333" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1333" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1334" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1334" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1334" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1334" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1335" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1335" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1335" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1335" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1336" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1336" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1336" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1336" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1337" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1337" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1337" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1337" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1338" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1338" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1338" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1338" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1339" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1339" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1339" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1339" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>2024-06-15</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1340" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1340" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1340" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1340" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>2024-06-15</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>charging;</t>
+        </is>
+      </c>
+      <c r="E1341" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1341" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1341" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1341" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>2024-06-15</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1342" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1342" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1342" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1342" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>2024-06-15</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1343" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1343" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1343" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1343" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1344" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1344" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1344" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1344" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1345" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1345" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1345" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1345" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1346" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1346" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1346" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1346" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1347" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1347" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1347" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1347" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1348" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1348" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1348" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1348" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1349" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1349" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1349" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1349" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1350" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1350" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1350" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1350" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1351" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1351" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1351" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1351" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1352" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1352" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1352" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1352" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1353" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1353" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1353" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1353" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1354" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1354" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1354" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1354" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>01:30:00</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1355" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1355" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1355" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1355" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1356" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1356" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1356" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1356" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1357" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1357" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1357" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1357" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1358" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1358" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1358" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1358" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1359" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1359" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1359" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1359" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>01:30:00</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1360" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1360" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1360" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1360" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>charging;</t>
+        </is>
+      </c>
+      <c r="E1361" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1361" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1361" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1361" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1362" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1362" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1362" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1362" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1363" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1363" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1363" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1363" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>00:00:00</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1364" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1364" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1364" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1364" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>01:30:00</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1365" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1365" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1365" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1365" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>discharging;</t>
+        </is>
+      </c>
+      <c r="E1366" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1366" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1366" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1366" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1367" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1367" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1367" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1367" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>Plugged</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>charged;</t>
+        </is>
+      </c>
+      <c r="E1368" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="F1368" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1368" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H1368" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
